--- a/out/НДС_по_5_юрлицам_2026_доходы_помесячно.xlsx
+++ b/out/НДС_по_5_юрлицам_2026_доходы_помесячно.xlsx
@@ -7,11 +7,12 @@
   </bookViews>
   <sheets>
     <sheet name="НДС по юрлицам" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Доходы 2026 по месяцам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Пояснения" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="актив про " sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="лгкие деньки " sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="рожков " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Пороги и риски" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Доходы 2026 по месяцам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Пояснения" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="актив про " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="лгкие деньки " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="рожков " sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -20,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,8 +137,15 @@
       <color indexed="21"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -163,6 +172,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -266,7 +280,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -535,6 +549,16 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1090,7 +1114,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Плательщик НДС</t>
+          <t>Плательщик НДС (с 2024 г., по данным компании)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1122,9 +1146,15 @@
         <f>'Доходы 2026 по месяцам'!N2</f>
         <v/>
       </c>
-      <c r="K3" s="6">
-        <f>'Доходы 2026 по месяцам'!P2</f>
-        <v/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Не применяется — уже плательщик НДС</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ставка 5 % действует, пока доход с начала года ≤ 272,5 млн руб. При превышении — 7 % с 1-го числа следующего месяца. См. лист «Пороги и риски».</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="99.75" customHeight="1">
@@ -1286,6 +1316,380 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="96" t="inlineStr">
+        <is>
+          <t>Пороги НДС на УСН в 2026 году</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Освобождение от НДС, руб.</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ставка 5 % — доход до, руб.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>272500000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ставка 7 % — доход до (и лимит УСН), руб.</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>490500000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Прошло месяцев 2026 (данные по)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="97" t="inlineStr">
+        <is>
+          <t>Юрлицо</t>
+        </is>
+      </c>
+      <c r="B7" s="97" t="inlineStr">
+        <is>
+          <t>Ставка НДС сейчас</t>
+        </is>
+      </c>
+      <c r="C7" s="97" t="inlineStr">
+        <is>
+          <t>Доход янв–сен 2026</t>
+        </is>
+      </c>
+      <c r="D7" s="97" t="inlineStr">
+        <is>
+          <t>Средний доход в месяц</t>
+        </is>
+      </c>
+      <c r="E7" s="97" t="inlineStr">
+        <is>
+          <t>Прогноз на год (по среднему)</t>
+        </is>
+      </c>
+      <c r="F7" s="97" t="inlineStr">
+        <is>
+          <t>Ближайший порог</t>
+        </is>
+      </c>
+      <c r="G7" s="97" t="inlineStr">
+        <is>
+          <t>Запас до порога</t>
+        </is>
+      </c>
+      <c r="H7" s="97" t="inlineStr">
+        <is>
+          <t>Сколько месяцев выдержит при среднем доходе</t>
+        </is>
+      </c>
+      <c r="I7" s="97" t="inlineStr">
+        <is>
+          <t>Риск</t>
+        </is>
+      </c>
+      <c r="J7" s="97" t="inlineStr">
+        <is>
+          <t>Доход за последний месяц (сентябрь)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ИП Рожков</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="C8" s="98">
+        <f>'Доходы 2026 по месяцам'!N2</f>
+        <v/>
+      </c>
+      <c r="D8" s="98">
+        <f>C8/$B$5</f>
+        <v/>
+      </c>
+      <c r="E8" s="98">
+        <f>D8*12</f>
+        <v/>
+      </c>
+      <c r="F8" s="98">
+        <f>$B$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="98">
+        <f>F8-C8</f>
+        <v/>
+      </c>
+      <c r="H8" s="99">
+        <f>IF(D8=0,"нет поступлений",G8/D8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(G8&lt;=0,"ПОРОГ ПРЕВЫШЕН",IF(OR(E8&gt;F8,AND(J8&gt;0,G8&lt;J8)),"ВЫСОКИЙ: может превысить в ближайший месяц / до конца года",IF(E8&gt;F8*0.8,"СРЕДНИЙ: прогноз больше 80 % порога","НИЗКИЙ")))</f>
+        <v/>
+      </c>
+      <c r="J8" s="98">
+        <f>'Доходы 2026 по месяцам'!J2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Легкие деньки</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="C9" s="98">
+        <f>'Доходы 2026 по месяцам'!N3</f>
+        <v/>
+      </c>
+      <c r="D9" s="98">
+        <f>C9/$B$5</f>
+        <v/>
+      </c>
+      <c r="E9" s="98">
+        <f>D9*12</f>
+        <v/>
+      </c>
+      <c r="F9" s="98">
+        <f>$B$2</f>
+        <v/>
+      </c>
+      <c r="G9" s="98">
+        <f>F9-C9</f>
+        <v/>
+      </c>
+      <c r="H9" s="99">
+        <f>IF(D9=0,"нет поступлений",G9/D9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(G9&lt;=0,"ПОРОГ ПРЕВЫШЕН",IF(OR(E9&gt;F9,AND(J9&gt;0,G9&lt;J9)),"ВЫСОКИЙ: может превысить в ближайший месяц / до конца года",IF(E9&gt;F9*0.8,"СРЕДНИЙ: прогноз больше 80 % порога","НИЗКИЙ")))</f>
+        <v/>
+      </c>
+      <c r="J9" s="98">
+        <f>'Доходы 2026 по месяцам'!J3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Актив Про</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Без НДС</t>
+        </is>
+      </c>
+      <c r="C10" s="98">
+        <f>'Доходы 2026 по месяцам'!N5</f>
+        <v/>
+      </c>
+      <c r="D10" s="98">
+        <f>C10/$B$5</f>
+        <v/>
+      </c>
+      <c r="E10" s="98">
+        <f>D10*12</f>
+        <v/>
+      </c>
+      <c r="F10" s="98">
+        <f>$B$2</f>
+        <v/>
+      </c>
+      <c r="G10" s="98">
+        <f>F10-C10</f>
+        <v/>
+      </c>
+      <c r="H10" s="99">
+        <f>IF(D10=0,"нет поступлений",G10/D10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(G10&lt;=0,"ПОРОГ ПРЕВЫШЕН",IF(OR(E10&gt;F10,AND(J10&gt;0,G10&lt;J10)),"ВЫСОКИЙ: может превысить в ближайший месяц / до конца года",IF(E10&gt;F10*0.8,"СРЕДНИЙ: прогноз больше 80 % порога","НИЗКИЙ")))</f>
+        <v/>
+      </c>
+      <c r="J10" s="98">
+        <f>'Доходы 2026 по месяцам'!J5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Эль Карго</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Без НДС (нет данных)</t>
+        </is>
+      </c>
+      <c r="C11" s="98">
+        <f>'Доходы 2026 по месяцам'!N4</f>
+        <v/>
+      </c>
+      <c r="D11" s="98">
+        <f>C11/$B$5</f>
+        <v/>
+      </c>
+      <c r="E11" s="98">
+        <f>D11*12</f>
+        <v/>
+      </c>
+      <c r="F11" s="98">
+        <f>$B$2</f>
+        <v/>
+      </c>
+      <c r="G11" s="98">
+        <f>F11-C11</f>
+        <v/>
+      </c>
+      <c r="H11" s="99">
+        <f>IF(D11=0,"нет поступлений",G11/D11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(G11&lt;=0,"ПОРОГ ПРЕВЫШЕН",IF(OR(E11&gt;F11,AND(J11&gt;0,G11&lt;J11)),"ВЫСОКИЙ: может превысить в ближайший месяц / до конца года",IF(E11&gt;F11*0.8,"СРЕДНИЙ: прогноз больше 80 % порога","НИЗКИЙ")))</f>
+        <v/>
+      </c>
+      <c r="J11" s="98">
+        <f>'Доходы 2026 по месяцам'!J4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="100" t="inlineStr">
+        <is>
+          <t>Риски</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="101" t="inlineStr">
+        <is>
+          <t>1. ИП Рожков, переход на 7 %. Порог 5 % в 2026 году — 272,5 млн руб. дохода с начала года. На 30.09 доход ≈147,4 млн, в среднем ≈16,4 млн в месяц, прогноз на год ≈196,5 млн. Запас ≈125 млн: порог перейдут, только если в октябре–декабре будет больше 40 млн в месяц. Если перейдут, ставка 7 % действует с 1-го числа следующего месяца, её надо закладывать в калькуляторы закупок. Контролировать ежемесячно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="75" customHeight="1">
+      <c r="A15" s="101" t="inlineStr">
+        <is>
+          <t>2. ИП Рожков, счёт 55.03. Через 55.03 проходит 115–285 млн в месяц (всего ≈1,5 млрд за 9 месяцев). Я считал это переводами между своими счетами (сколько пришло, столько и ушло). Если это выручка (эквайринг, маркетплейс, платёжный агент), доход превысит и порог 7 % (490,5 млн), и лимит УСН — будут ОСНО и НДС 22 %. Бухгалтеру надо подтвердить, что это за счёт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="101" t="inlineStr">
+        <is>
+          <t>3. ИП Рожков, «платим с 2024 года». Ставки 5 %/7 % на УСН появились только с 01.01.2025, до этого ИП на УСН не платил НДС (кроме как по счетам-фактурам с выделенным НДС и при импорте). Если в 2024 году НДС платили, значит был другой режим (ОСНО) — это стоит пояснить финдиректору. 5 % без вычетов выбирается на 12 кварталов подряд: с 2025 года отказаться от неё можно не раньше 2028 года.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="101" t="inlineStr">
+        <is>
+          <t>4. ИП Рожков, вычетов нет. При 5 % входной НДС поставщиков не принимается к вычету, он входит в стоимость закупки. В калькуляторах закупок цена поставщика берётся вместе с НДС, а 5 % начисляется на цену продажи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="75" customHeight="1">
+      <c r="A18" s="101" t="inlineStr">
+        <is>
+          <t>5. Легкие деньки, высокий риск. Только в сентябре поступило 13,5 млн, всего 14,6 млн, до 20 млн осталось ≈5,4 млн. Если это превысят в октябре, НДС будет с 01.11.2026: надо выбрать ставку (5 % без вычетов или 22 % с вычетами) и выставлять счета-фактуры. С 1-го числа следующего месяца цену в договорах и калькуляторах надо считать с НДС.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="75" customHeight="1">
+      <c r="A19" s="101" t="inlineStr">
+        <is>
+          <t>6. Актив Про: ≈8 млн за 9 месяцев, риск низкий, но через 55.03 проходят большие суммы (до 79 млн в месяц) — проверить, как в п. 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="75" customHeight="1">
+      <c r="A20" s="101" t="inlineStr">
+        <is>
+          <t>7. Эль Карго: нет выписки за 2026 год, риск оценить нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
+      <c r="A21" s="101" t="inlineStr">
+        <is>
+          <t>8. Порог 20 млн с 2027 года снижается до 15 млн, с 2028 — до 10 млн. Дальше пороги будут индексироваться: значения на следующий год нужно сверять с ФНС.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A16:I16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1589,7 +1993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1676,7 +2080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4157,7 +4561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6234,7 +6638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/out/НДС_по_5_юрлицам_2026_доходы_помесячно.xlsx
+++ b/out/НДС_по_5_юрлицам_2026_доходы_помесячно.xlsx
@@ -8,11 +8,12 @@
   <sheets>
     <sheet name="НДС по юрлицам" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Пороги и риски" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Доходы 2026 по месяцам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Пояснения" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="актив про " sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="лгкие деньки " sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="рожков " sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Чек-лист" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Доходы 2026 по месяцам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Пояснения" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="актив про " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="лгкие деньки " sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="рожков " sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -145,7 +146,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -177,6 +178,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -280,7 +291,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -557,6 +568,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1695,6 +1712,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="96" t="inlineStr">
+        <is>
+          <t>Чек-лист по задаче «Ставка НДС по юрлицам»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="97" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="97" t="inlineStr">
+        <is>
+          <t>Что сделать</t>
+        </is>
+      </c>
+      <c r="C3" s="97" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="D3" s="97" t="inlineStr">
+        <is>
+          <t>Кто</t>
+        </is>
+      </c>
+      <c r="E3" s="97" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="101" t="inlineStr">
+        <is>
+          <t>Доходы 2026 по месяцам: Рожков, Легкие деньки, Актив Про</t>
+        </is>
+      </c>
+      <c r="C4" s="102" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="D4" s="101" t="inlineStr"/>
+      <c r="E4" s="101" t="inlineStr">
+        <is>
+          <t>Лист «Доходы 2026 по месяцам», источник — анализ сч. 51 из 1С</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="101" t="inlineStr">
+        <is>
+          <t>Ставка НДС по 4 юрлицам</t>
+        </is>
+      </c>
+      <c r="C5" s="102" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="D5" s="101" t="inlineStr"/>
+      <c r="E5" s="101" t="inlineStr">
+        <is>
+          <t>Аргумент 22 %, Рожков 5 %, Легкие деньки и Эль Карго — без НДС</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="101" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="101" t="inlineStr">
+        <is>
+          <t>Пороги 5 % / 7 % / 20 млн и риски</t>
+        </is>
+      </c>
+      <c r="C6" s="102" t="inlineStr">
+        <is>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="D6" s="101" t="inlineStr"/>
+      <c r="E6" s="101" t="inlineStr">
+        <is>
+          <t>Лист «Пороги и риски»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="101" t="inlineStr">
+        <is>
+          <t>Добавить 5-е юрлицо</t>
+        </is>
+      </c>
+      <c r="C7" s="103" t="inlineStr">
+        <is>
+          <t>Не сделано</t>
+        </is>
+      </c>
+      <c r="D7" s="101" t="inlineStr"/>
+      <c r="E7" s="101" t="inlineStr">
+        <is>
+          <t>В задании пять юрлиц, в таблице четыре</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="101" t="inlineStr">
+        <is>
+          <t>Выгрузить из 1С анализ сч. 51 по Эль Карго за 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="103" t="inlineStr">
+        <is>
+          <t>Не сделано</t>
+        </is>
+      </c>
+      <c r="D8" s="101" t="inlineStr"/>
+      <c r="E8" s="101" t="inlineStr">
+        <is>
+          <t>Без него риск по порогу 20 млн не оценить</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="101" t="inlineStr">
+        <is>
+          <t>Подтвердить у бухгалтера, что за счёт 55.03 у Рожкова и Актив Про</t>
+        </is>
+      </c>
+      <c r="C9" s="103" t="inlineStr">
+        <is>
+          <t>Не сделано</t>
+        </is>
+      </c>
+      <c r="D9" s="101" t="inlineStr">
+        <is>
+          <t>Бухгалтер</t>
+        </is>
+      </c>
+      <c r="E9" s="101" t="inlineStr">
+        <is>
+          <t>Если это выручка — у Рожкова превышен лимит УСН, НДС 22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="101" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="101" t="inlineStr">
+        <is>
+          <t>Пояснить режим Рожкова в 2024 году</t>
+        </is>
+      </c>
+      <c r="C10" s="103" t="inlineStr">
+        <is>
+          <t>Не сделано</t>
+        </is>
+      </c>
+      <c r="D10" s="101" t="inlineStr"/>
+      <c r="E10" s="101" t="inlineStr">
+        <is>
+          <t>Ставка 5 % на УСН действует только с 2025 г.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="101" t="inlineStr">
+        <is>
+          <t>Легкие деньки: заранее выбрать ставку на случай превышения 20 млн (5 % или 22 %)</t>
+        </is>
+      </c>
+      <c r="C11" s="103" t="inlineStr">
+        <is>
+          <t>Не сделано</t>
+        </is>
+      </c>
+      <c r="D11" s="101" t="inlineStr">
+        <is>
+          <t>Финдиректор</t>
+        </is>
+      </c>
+      <c r="E11" s="101" t="inlineStr">
+        <is>
+          <t>Запас 5,4 млн; при превышении в октябре — НДС с 01.11.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="101" t="inlineStr">
+        <is>
+          <t>Поставить верную ставку в калькулятор по Чечне (КД-8)</t>
+        </is>
+      </c>
+      <c r="C12" s="103" t="inlineStr">
+        <is>
+          <t>Не сделано</t>
+        </is>
+      </c>
+      <c r="D12" s="101" t="inlineStr"/>
+      <c r="E12" s="101" t="inlineStr">
+        <is>
+          <t>Ставка того юрлица, через которое идёт закупка (у Рожкова 5 %, не 22 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="101" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="101" t="inlineStr">
+        <is>
+          <t>Обновлять доходы каждый месяц</t>
+        </is>
+      </c>
+      <c r="C13" s="101" t="inlineStr">
+        <is>
+          <t>Регулярно</t>
+        </is>
+      </c>
+      <c r="D13" s="101" t="inlineStr"/>
+      <c r="E13" s="101" t="inlineStr">
+        <is>
+          <t>Особенно Легкие деньки (порог 20 млн) и Рожков (порог 7 % — 272,5 млн)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Готово,Не сделано,В работе,Регулярно"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1993,7 +2288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2080,7 +2375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4561,7 +4856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6638,7 +6933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
